--- a/Översikt VÅRGÅRDA.xlsx
+++ b/Översikt VÅRGÅRDA.xlsx
@@ -601,7 +601,7 @@
         <v>44628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45254</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>44992</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45911</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45752</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>45937</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45936</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>45989</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>46036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>45203</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>46059</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>46066</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>45008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>45752</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>46273</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45373</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>44693</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44496</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44511</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44568</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44601</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44533</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>44572</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>44496</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>44677</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44818</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>44571</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>44501</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>44505</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>44743</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44607</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>44580</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>44511</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>44811</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>44616</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>44621</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>44465</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>44469</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44501</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>44573</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44826</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44662</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44648</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44515</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45040</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>45315</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44907</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45751</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44510</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45469</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44984</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>45327</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>45329</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44946</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45357</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45620</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45233</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45363</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>44725</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44463</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45374</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45351</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45375</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45247</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45362</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45443</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>45400</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45110</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45189</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>44846</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44881</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45357</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45357</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45180</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45772</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44920</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44984</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45446</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>45565</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44739</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44914</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45735</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>46030</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>45354</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>45084</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>45180</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44908</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>45446</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>45443</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44936</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45397</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45891</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44943</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45134</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45429</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45429</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>45901</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>46036</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44905</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45772</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45852</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>45756</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>45910</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>45910</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45910</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>44984</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45366</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44568</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45105</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>45987</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>45923</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>45920</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45920</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45925</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>45925</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45406</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>45084</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45925</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>44922</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>45926</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45927</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>44951</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45933</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>45933</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45932</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45726</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45933</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45932</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45401</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45932</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44964</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>45933</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>45247</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>45715</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>45330</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>45938</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>45397</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45397</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>45212</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>45947</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45608</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45112</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>45968</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>45968</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45973</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45972</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45972</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>45974</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>45406</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>45210</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>45040</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45985</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>45985</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>45985</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>45989</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>45988</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>45989</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>44968</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>45988</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>45268</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>45751</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>46031</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>46031</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45999</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45999</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45721</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45189</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>44511</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>44518</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>46002</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45756</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45693</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45301</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45703</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45706</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45327</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>46170</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>46170</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45260</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>46031</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>46170</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>46035</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>46032</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>46031</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>46032</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>46034</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45972</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>46036</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>46036</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>46036</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>46036</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>44900</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>46036</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>46038</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>46038</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>46042</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>46043</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45062</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45751</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>45751</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>46051</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>46051</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>44608</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45058</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45616</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>46178</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>45253</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>46059</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>45363</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>46059</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>46058</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>44960</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>45375</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>44910</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>45356</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>46064</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45210</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>46066</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>46070</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>46070</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>46070</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>46070</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>44713</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>44713</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45163</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>46086</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>46085</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>45237</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>45600</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44900</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45375</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>45612</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>46091</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>44900</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44950</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>44791</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45189</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>46101</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>46199</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>46106</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>45587</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>44917</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>44917</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>44952</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>46114</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>46114</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>45350</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>46124</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>46124</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>46126</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>46126</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>46125</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>46126</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>46127</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44517</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45208</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45826</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>46133</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>46134</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>46135</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>45664</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>46134</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44865</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>46246</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>46246</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44655</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>45233</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45751</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>46246</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>44942</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>46205</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>46205</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>46248</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>45190</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45906</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>46252</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45273</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>46197</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>46211</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>45159</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45769</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>45057</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>46259</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45385</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>46260</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>44895</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>46265</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>46124</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>44811</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45198</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>45491</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>45198</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>46269</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45782</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>46268</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>46276</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>46276</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>46281</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45796</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>46240</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45576</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45800</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45692</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45800</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45804</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>45804</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45804</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>45253</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45811</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45811</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>45233</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>45812</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45812</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>45817</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45774</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>45616</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45471</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45734</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>45734</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>45573</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>45859</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>45625</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45870</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45538</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>45776</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45769</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>44628</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45323</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>45317</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45345</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45345</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>45606</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45373</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45565</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45482</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45323</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>46094</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>46093</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>46077</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>

--- a/Översikt VÅRGÅRDA.xlsx
+++ b/Översikt VÅRGÅRDA.xlsx
@@ -601,7 +601,7 @@
         <v>44628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45254</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>44992</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>46036</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>45911</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>46059</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>46066</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>45936</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>45757</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>45203</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>45752</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>45755</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>46287</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45752</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>44693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>44568</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44601</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44533</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44496</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44818</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44571</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44501</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44743</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44607</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44580</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44511</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44811</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>44465</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44469</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44501</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44573</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44826</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44662</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44648</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44515</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45058</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44739</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45105</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>45375</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>44900</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45330</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45385</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>45772</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45400</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45253</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45327</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45268</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44811</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>45443</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45693</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45443</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45247</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44865</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45796</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44846</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44942</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45576</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44920</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45163</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44984</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>46032</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>45776</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>46031</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>46032</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45972</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>46034</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45800</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>46035</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45397</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>46036</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45357</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>46036</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>46038</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>46036</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>46038</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>46036</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>46036</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>46042</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45891</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>46043</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45852</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45800</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>46051</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>45356</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>45910</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>45910</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>46051</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>44900</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45910</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>46058</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>46059</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>46059</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45804</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45804</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45692</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>46064</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45350</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>46066</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45920</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45401</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45920</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45751</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>45751</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>46070</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>46070</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>46070</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45804</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45923</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>46070</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45925</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>45925</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45925</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>45212</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>45927</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45926</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>44951</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45253</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45233</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>46085</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45933</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>46086</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44917</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44917</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>45933</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>45933</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>45932</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>45932</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>45932</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>45933</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>46091</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>44905</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>45938</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>45366</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>44725</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44936</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>45210</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44900</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>46101</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>45812</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44950</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45600</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45947</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45112</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>46106</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>44713</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>44713</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>46114</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>46114</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>45565</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>45811</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>45811</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>46124</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>44960</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>46125</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>46126</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>46127</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45968</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45968</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45972</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45972</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45973</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45974</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>46126</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>46126</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>45616</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45608</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>46134</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>46134</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>46133</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45471</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>45985</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>45985</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45985</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45988</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>45988</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>46135</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45989</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45989</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>45901</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>46031</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45446</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>46031</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>44984</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>44908</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>45999</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>45999</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>45774</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>45198</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>45726</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>46002</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45817</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>44914</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45491</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45084</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>44881</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44568</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45406</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>45987</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>45703</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>45706</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>45354</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44943</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>46036</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>46030</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>45734</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>45769</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>45057</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>45751</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45233</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45721</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45734</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44791</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45751</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>45351</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>45363</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>45573</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>44510</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>45374</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>45375</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>44511</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45859</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>46170</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45110</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>46170</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>46170</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>45357</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>45357</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45062</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>45625</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45446</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>44910</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45134</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45870</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>46178</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45715</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>45040</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45040</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>44518</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>45327</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>45189</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>45180</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>45538</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
         <v>46199</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44608</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         <v>45769</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>46205</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>46205</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>45826</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>46197</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>45587</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45906</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>46252</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>44655</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>46211</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45233</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45260</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>45198</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45198</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>46259</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>46260</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45756</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>46124</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>46265</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45612</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45772</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>46268</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>46269</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45362</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>44907</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45751</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>46276</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45159</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>46276</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45735</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45756</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45301</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>44946</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>46281</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>44964</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>46240</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45406</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>46287</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46288</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>46246</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>46246</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>46246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45180</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>46290</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>44984</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46290</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>46248</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>46287</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45363</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>44895</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46290</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>46290</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>44922</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45210</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>45429</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>45429</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45247</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>45375</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45620</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44952</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45189</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45237</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45664</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45208</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>45084</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>44968</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>45273</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>45397</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>45397</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45469</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45189</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45315</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>45329</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45190</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45782</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>44628</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45323</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45317</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45345</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45345</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45606</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45373</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45565</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45482</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45323</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46093</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>46094</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>46077</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>

--- a/Översikt VÅRGÅRDA.xlsx
+++ b/Översikt VÅRGÅRDA.xlsx
@@ -601,7 +601,7 @@
         <v>44628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45254</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>44992</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>46036</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>45911</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>46059</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>46066</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>45936</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>45757</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>45203</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>45752</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>45755</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>46287</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45752</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>44693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>44568</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44601</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44533</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44496</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44818</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44571</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44501</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44743</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44607</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44580</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44511</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44811</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>44465</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44469</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44501</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44573</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44826</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44662</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44648</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44515</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45058</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44739</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45105</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>45375</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>44900</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45330</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45385</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>45772</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45400</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45253</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45327</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45268</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44811</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44517</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>45443</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45693</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45443</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45247</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44865</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45796</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44846</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44942</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45576</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44920</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45163</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44984</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>46032</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>45776</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>46031</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>46032</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45972</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>46034</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45800</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>46035</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45397</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>46036</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45357</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>46036</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>46038</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>46036</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>46038</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>46036</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>46036</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>46042</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45891</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>46043</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45852</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45800</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>46051</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>45356</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>45910</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>45910</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>46051</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>44900</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45910</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>46058</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>46059</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>46059</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45804</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45804</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45692</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>46064</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45350</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>46066</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45920</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45401</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45920</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45751</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>45751</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>46070</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>46070</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>46070</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45804</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45923</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>46070</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45925</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>45925</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45925</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>45212</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>45927</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45926</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>44951</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45253</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45233</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>46085</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45933</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>46086</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44917</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44917</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>45933</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>45933</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>45932</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>45932</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>45932</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>45933</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>46091</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>44905</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>45938</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>45366</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>44725</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44936</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>45210</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44900</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>46101</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>45812</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44950</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45600</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45947</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45112</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>46106</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>44713</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>44713</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>46114</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>46114</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>45565</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>45811</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>45811</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>46124</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>44960</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>46125</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>46126</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>46127</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45968</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45968</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45972</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45972</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45973</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45974</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>46126</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>46126</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>45616</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45608</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>46134</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>46134</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>46133</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45471</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>45985</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>45985</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45985</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45988</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>45988</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>46135</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45989</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45989</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>45901</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>46031</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45446</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>46031</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>44984</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>44908</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>45999</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>45999</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>45774</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>45198</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>45726</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>46002</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45817</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>44914</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45491</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45084</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>44881</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44568</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45406</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>45987</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>45703</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>45706</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>45354</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44943</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>46036</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>46030</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>45734</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>45769</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>45057</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>45751</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45233</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45721</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45734</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44791</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45751</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>45351</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>45363</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>45573</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>44510</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>45374</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>45375</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>44511</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45859</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>46170</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45110</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>46170</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>46170</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>45357</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>45357</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45062</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>45625</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45446</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>44910</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45134</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45870</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>46178</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45715</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>45040</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45040</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>44518</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>45327</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>45189</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>45180</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>45538</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
         <v>46199</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44608</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         <v>45769</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>46205</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>46205</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>45826</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>46197</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>45587</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45906</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>46252</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>44655</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>46211</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45233</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45260</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>45198</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45198</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>46259</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>46260</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45756</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>46124</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>46265</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45612</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45772</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>46268</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>46269</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45362</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>44907</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45751</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>46276</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45159</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>46276</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45735</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45756</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45301</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>44946</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>46281</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>44964</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>46240</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45406</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>46287</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46288</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>46246</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>46246</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>46246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45180</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>46290</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>44984</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46290</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>46248</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>46287</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45363</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>44895</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46290</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>46290</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>44922</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45210</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>45429</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>45429</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45247</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>45375</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45620</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44952</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45189</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45237</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45664</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45208</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>45084</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>44968</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>45273</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>45397</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>45397</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45469</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45189</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45315</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>45329</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45190</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45782</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>44628</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45323</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45317</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45345</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45345</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45606</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45373</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45565</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45482</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45323</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46093</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>46094</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>46077</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>

--- a/Översikt VÅRGÅRDA.xlsx
+++ b/Översikt VÅRGÅRDA.xlsx
@@ -601,7 +601,7 @@
         <v>44628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45254</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46036</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45911</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>46059</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>46066</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>45937</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45936</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45989</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45755</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45752</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44992</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>45203</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45008</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>46287</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>45757</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45752</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>44693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>44568</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44601</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44533</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44496</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44818</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44571</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44501</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44743</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44607</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44580</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44511</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44811</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>44501</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44573</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44662</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44648</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44515</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45751</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>44510</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>45040</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45469</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>45315</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44984</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>44907</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45327</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45329</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>44946</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>46002</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45357</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45620</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45233</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45363</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45693</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>45703</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45706</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>44725</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45397</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>45891</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>46035</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45901</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46032</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>46031</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>46032</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>46034</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45972</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>46036</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>46036</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>46036</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>46036</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45374</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>46036</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45375</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>46038</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>46038</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>45351</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>46042</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>46043</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>45910</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45796</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45910</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45910</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>45247</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45576</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>46051</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>45800</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>45692</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>45800</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>46051</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45804</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45804</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>45804</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45253</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>45923</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45920</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>45920</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45362</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45925</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45925</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>46059</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>46059</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45443</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45926</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45927</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>46058</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45933</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45932</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45932</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>46064</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45932</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45933</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45938</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>46066</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>46070</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>46070</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>46070</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45400</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>46070</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45811</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45811</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>45947</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>45233</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45110</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>46086</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>46085</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45812</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>45812</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45189</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>44846</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>44881</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>46091</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45817</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45774</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45357</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45357</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45772</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45968</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45180</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45968</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45973</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>44900</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>44950</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45972</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45972</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45974</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>44920</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>46101</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45616</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45446</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>46106</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>44984</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>45471</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45565</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45985</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>45985</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45985</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>44739</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>46114</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>46114</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>45989</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>45988</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>45989</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>45988</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>45734</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>46124</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>46031</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>46126</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>46126</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>46125</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>46031</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45735</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45999</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45999</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>46126</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>46127</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45084</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>45180</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>46133</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>45443</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>44936</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>46134</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>46135</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>46134</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45734</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>45901</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>44943</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45134</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>45429</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45429</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>44905</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45772</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44914</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>46030</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45354</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45756</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45573</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>44984</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>44908</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45366</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45446</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>45105</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>45084</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>46036</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44922</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>44951</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45859</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45726</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45401</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>44964</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>45625</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45247</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45715</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45330</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45397</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45397</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44568</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45987</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45406</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45212</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45608</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45870</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45112</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45406</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45210</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>45040</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45538</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>46170</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>46170</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>46170</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>44968</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45776</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>45769</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>46178</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>45268</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         <v>45751</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45721</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45189</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44511</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>44518</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45756</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>46199</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45301</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>45327</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45826</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>45260</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>46205</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>46205</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>44900</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>45906</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>46197</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>46211</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45062</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45751</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>45751</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>46259</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>46260</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>44608</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45058</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>46265</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>46124</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>45253</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>45363</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>44960</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>45375</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44910</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>45356</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>45210</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>46269</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>44713</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>44713</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>46268</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>45163</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>46276</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>46276</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45237</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>46281</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>45600</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>44900</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45375</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>45612</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>45198</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>46240</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>44791</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>45189</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>45587</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>44917</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44917</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>44952</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>46288</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46287</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>46246</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>46246</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45350</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>46246</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>46248</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>44517</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45208</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>46290</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>46290</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46290</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>46287</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>46290</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45664</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44865</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>46252</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>46294</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44655</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45233</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45751</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45925</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>45933</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44942</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>46296</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45190</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>45273</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45159</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45769</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45057</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45385</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>44895</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>44811</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>45198</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>45491</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45198</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45782</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44628</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45323</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45317</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45345</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45345</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45606</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45373</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45565</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45482</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45323</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>46094</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>46093</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>46077</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>

--- a/Översikt VÅRGÅRDA.xlsx
+++ b/Översikt VÅRGÅRDA.xlsx
@@ -601,7 +601,7 @@
         <v>44628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45254</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46036</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45911</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>46059</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>46066</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>45937</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45936</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45989</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45755</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45752</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44992</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>45203</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45008</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>46287</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>45757</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45752</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>44693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>44568</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44601</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44533</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44496</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44818</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44571</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44501</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44743</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44607</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44580</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44511</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44811</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>44501</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44573</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44662</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44648</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44515</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45751</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>44510</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>45040</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45469</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>45315</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44984</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>44907</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45327</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45329</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>44946</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>46002</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45357</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45620</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45233</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45363</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45693</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>45703</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45706</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>44725</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45397</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>45891</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>46035</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45901</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46032</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>46031</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>46032</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>46034</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45972</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>46036</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>46036</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>46036</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>46036</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45374</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>46036</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45375</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>46038</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>46038</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>45351</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>46042</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>46043</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>45910</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45796</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45910</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45910</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>45247</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45576</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>46051</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>45800</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>45692</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>45800</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>46051</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45804</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45804</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>45804</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45253</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>45923</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45920</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>45920</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45362</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45925</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45925</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>46059</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>46059</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45443</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45926</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45927</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>46058</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45933</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45932</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45932</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>46064</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45932</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45933</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45938</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>46066</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>46070</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>46070</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>46070</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45400</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>46070</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45811</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45811</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>45947</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>45233</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45110</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>46086</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>46085</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45812</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>45812</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45189</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>44846</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>44881</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>46091</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45817</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45774</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45357</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45357</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45772</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45968</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45180</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45968</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45973</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>44900</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>44950</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45972</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45972</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45974</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>44920</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>46101</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45616</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45446</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>46106</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>44984</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>45471</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45565</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45985</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>45985</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45985</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>44739</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>46114</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>46114</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>45989</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>45988</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>45989</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>45988</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>45734</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>46124</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>46031</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>46126</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>46126</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>46125</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>46031</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45735</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45999</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45999</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>46126</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>46127</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45084</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>45180</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>46133</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>45443</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>44936</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>46134</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>46135</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>46134</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45734</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>45901</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>44943</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45134</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>45429</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45429</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>44905</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45772</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44914</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>46030</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45354</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45756</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45573</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>44984</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>44908</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45366</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45446</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>45105</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>45084</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>46036</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44922</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>44951</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45859</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45726</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45401</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>44964</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>45625</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45247</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45715</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45330</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45397</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45397</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44568</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45987</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45406</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45212</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45608</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45870</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45112</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45406</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45210</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>45040</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45538</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>46170</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>46170</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>46170</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>44968</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45776</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>45769</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>46178</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>45268</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         <v>45751</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45721</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45189</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44511</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>44518</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45756</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>46199</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45301</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>45327</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45826</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>45260</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>46205</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>46205</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>44900</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>45906</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>46197</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>46211</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45062</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45751</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>45751</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>46259</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>46260</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>44608</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45058</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>46265</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>46124</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>45253</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>45363</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>44960</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>45375</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44910</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>45356</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>45210</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>46269</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>44713</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>44713</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>46268</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>45163</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>46276</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>46276</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45237</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>46281</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>45600</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>44900</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45375</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>45612</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>45198</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>46240</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>44791</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>45189</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>45587</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>44917</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44917</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>44952</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>46288</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46287</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>46246</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>46246</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45350</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>46246</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>46248</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>44517</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45208</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>46290</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>46290</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46290</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>46287</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>46290</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45664</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44865</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>46252</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>46294</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44655</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45233</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45751</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45925</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>45933</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44942</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>46296</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45190</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>45273</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45159</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45769</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45057</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45385</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>44895</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>44811</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>45198</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>45491</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45198</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45782</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44628</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45323</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45317</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45345</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45345</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45606</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45373</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45565</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45482</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45323</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>46094</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>46093</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>46077</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>

--- a/Översikt VÅRGÅRDA.xlsx
+++ b/Översikt VÅRGÅRDA.xlsx
@@ -601,7 +601,7 @@
         <v>44628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45254</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45752</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45752</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>44992</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45911</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>45008</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45936</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>45755</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>45203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46036</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46059</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>46066</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>46273</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>46287</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>44693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>44568</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44601</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44533</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44496</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44818</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44571</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44501</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44501</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44505</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44511</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44743</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44607</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44616</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44811</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44573</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>44826</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44580</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44621</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>45375</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44662</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44648</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44515</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44900</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45330</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44952</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45189</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>44791</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45385</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>45751</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45351</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>45363</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44739</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45058</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45237</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>45664</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>45772</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45208</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>45253</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45400</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45084</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45105</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>45327</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44968</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45273</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45268</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45769</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>45397</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45397</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>44510</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>44517</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>44811</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45374</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45375</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45443</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45469</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45443</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45247</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44865</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>44511</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45776</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45110</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45357</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45357</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>45062</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44846</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45397</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44942</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45189</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45446</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>44910</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44920</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>45163</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44984</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45891</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45315</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>45901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45357</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>45852</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45329</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>45134</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45190</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45910</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45910</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45910</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>45715</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>45040</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>45040</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>45782</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>44518</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>45356</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>44900</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45327</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>45189</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45180</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45920</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45920</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45350</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45401</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>45923</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>45751</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>45751</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>45925</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>45925</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>45212</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>45927</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>45926</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44951</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>45796</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>44608</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>45576</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>44917</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>44917</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>45800</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44905</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45933</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45933</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>45800</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45932</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>45932</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45932</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>45804</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>45804</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>45692</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45366</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>45804</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>44725</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>44936</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>45210</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>45253</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>45587</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>45233</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>45600</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45112</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44655</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45938</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45812</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45812</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45811</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45811</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>45616</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45471</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>44713</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44713</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45774</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45817</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>45565</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45947</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45233</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44960</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>45260</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45734</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>45198</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45198</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45734</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45608</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>45968</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>45968</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>45972</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45972</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>45973</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45756</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45974</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>45612</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>45573</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>44984</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45859</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45772</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>45198</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>45726</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>45625</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>45870</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>45491</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45084</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>45362</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>44881</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44907</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>45538</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45751</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44943</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>45159</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45735</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>45756</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>45985</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45985</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44900</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>45301</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>46101</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45985</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>44950</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44946</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45769</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>45988</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>46106</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17165,7 +17165,7 @@
         <v>45988</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>45057</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>45989</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>45989</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>44964</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>45751</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45233</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>46114</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>46114</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>46031</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>46031</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>46124</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45406</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>46125</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>46126</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>45999</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45999</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>46127</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>46126</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>46126</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>46002</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>46134</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>46134</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>46133</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>46135</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45180</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44984</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>45363</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>44895</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45901</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>45446</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45703</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>45706</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>45693</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>44908</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>44914</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>44922</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>46032</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>46031</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>46032</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45972</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>46034</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>46035</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>46036</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>46036</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44568</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>45406</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>46038</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>46036</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>46038</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>46036</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>46036</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>46042</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45987</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45210</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45354</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>46043</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>46036</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45429</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>45429</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45247</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>46030</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45375</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45620</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>46051</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>46051</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>46059</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>46059</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>46064</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>46066</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>46070</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>46070</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>46070</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>46070</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>46085</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>46086</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>46091</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>46170</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46170</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46170</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>46178</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>46199</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>46205</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>46205</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45826</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>46197</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45906</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46211</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>46124</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>46265</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>46268</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>46269</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46276</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>46276</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>46281</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>46240</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>46287</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>46288</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>46246</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>46246</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>46246</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>46290</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>46290</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>46290</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>46290</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>46294</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>46287</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>46248</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>46296</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>46252</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>45933</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45925</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>46259</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>46260</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>44628</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45323</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>45317</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45345</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45345</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45606</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45373</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>45565</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>45482</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45323</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>46093</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>46094</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>46077</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>

--- a/Översikt VÅRGÅRDA.xlsx
+++ b/Översikt VÅRGÅRDA.xlsx
@@ -601,7 +601,7 @@
         <v>44628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45254</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45752</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45752</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>44992</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45911</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>45008</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45936</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>45755</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>45203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46036</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46059</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>46066</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>46273</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>46287</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>44693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>44568</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44601</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44533</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44496</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44818</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44571</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44501</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44501</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44505</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44511</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44743</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44607</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44616</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44811</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44573</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>44826</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44580</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44621</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>45375</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44662</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44648</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44515</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44900</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45330</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44952</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45189</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>44791</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45385</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>45751</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45351</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>45363</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44739</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45058</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45237</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>45664</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>45772</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45208</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>45253</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45400</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45084</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45105</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>45327</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44968</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45273</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45268</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45769</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>45397</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45397</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>44510</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>44517</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>44811</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45374</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45375</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45443</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45469</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45443</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45247</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44865</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>44511</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45776</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45110</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45357</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45357</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>45062</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44846</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45397</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44942</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45189</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45446</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>44910</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44920</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>45163</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44984</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45891</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45315</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>45901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45357</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>45852</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45329</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>45134</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45190</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45910</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45910</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45910</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>45715</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>45040</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>45040</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>45782</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>44518</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>45356</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>44900</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45327</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>45189</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45180</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45920</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45920</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45350</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45401</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>45923</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>45751</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>45751</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>45925</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>45925</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>45212</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>45927</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>45926</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44951</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>45796</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>44608</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>45576</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>44917</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>44917</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>45800</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44905</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45933</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45933</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>45800</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45932</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>45932</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45932</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>45804</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>45804</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>45692</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45366</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>45804</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>44725</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>44936</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>45210</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>45253</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>45587</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>45233</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>45600</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45112</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44655</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45938</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45812</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45812</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45811</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45811</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>45616</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45471</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>44713</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44713</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45774</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45817</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>45565</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45947</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45233</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44960</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>45260</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45734</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>45198</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45198</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45734</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45608</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>45968</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>45968</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>45972</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45972</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>45973</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45756</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45974</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>45612</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>45573</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>44984</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45859</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45772</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>45198</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>45726</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>45625</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>45870</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>45491</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45084</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>45362</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>44881</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44907</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>45538</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45751</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44943</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>45159</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45735</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>45756</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>45985</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45985</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44900</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>45301</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>46101</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45985</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>44950</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44946</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45769</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>45988</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>46106</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17165,7 +17165,7 @@
         <v>45988</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>45057</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>45989</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>45989</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>44964</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>45751</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45233</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>46114</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>46114</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>46031</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>46031</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>46124</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45406</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>46125</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>46126</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>45999</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45999</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>46127</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>46126</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>46126</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>46002</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>46134</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>46134</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>46133</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>46135</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45180</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44984</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>45363</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>44895</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45901</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>45446</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45703</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>45706</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>45693</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>44908</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>44914</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>44922</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>46032</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>46031</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>46032</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45972</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>46034</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>46035</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>46036</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>46036</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44568</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>45406</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>46038</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>46036</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>46038</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>46036</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>46036</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>46042</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45987</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45210</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45354</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>46043</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>46036</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45429</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>45429</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45247</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>46030</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45375</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45620</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>46051</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>46051</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>46059</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>46059</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>46064</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>46066</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>46070</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>46070</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>46070</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>46070</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>46085</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>46086</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>46091</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>46170</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46170</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46170</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>46178</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>46199</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>46205</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>46205</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45826</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>46197</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45906</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46211</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>46124</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>46265</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>46268</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>46269</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46276</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>46276</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>46281</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>46240</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>46287</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>46288</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>46246</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>46246</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>46246</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>46290</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>46290</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>46290</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>46290</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>46294</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>46287</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>46248</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>46296</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>46252</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>45933</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45925</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>46259</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>46260</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>44628</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45323</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>45317</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45345</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45345</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45606</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45373</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>45565</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>45482</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45323</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>46093</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>46094</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>46077</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>

--- a/Översikt VÅRGÅRDA.xlsx
+++ b/Översikt VÅRGÅRDA.xlsx
@@ -601,7 +601,7 @@
         <v>44628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45254</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>44992</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45911</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45937</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>45755</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45752</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>45989</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>46036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>46059</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>46066</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>45203</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>45008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>45757</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>46287</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45752</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>44693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>44568</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44601</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44533</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44496</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44818</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44571</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44501</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44743</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44607</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44580</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44511</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44811</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>44501</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44573</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44662</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44648</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44515</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45040</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45315</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44907</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45751</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>45469</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>44984</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45327</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45329</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>45233</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45357</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45620</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44725</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45363</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44946</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45374</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>45375</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45351</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45247</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45362</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>45443</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45400</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45110</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45189</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44846</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44881</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45357</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45357</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45180</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>45772</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44920</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45446</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>44984</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45565</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44914</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44739</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>46030</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>45354</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44908</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45446</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45397</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45891</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45084</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45180</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>46036</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45443</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44936</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>44568</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45987</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>45852</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>45406</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>44943</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>45910</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45910</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>45910</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>45134</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>45429</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>45429</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>44905</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45772</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45923</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45920</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45920</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45925</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45756</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44984</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45366</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45927</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45105</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>45933</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45932</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45932</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45932</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45933</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45938</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>45084</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>44922</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>45947</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>44951</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>45726</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>45401</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>44964</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>45247</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45715</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45330</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>45397</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45397</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>45212</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>45968</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45968</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45973</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>45972</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>45608</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>45972</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45974</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45112</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45985</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45985</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>45985</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45989</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45988</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45989</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45988</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45406</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>46031</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>46031</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45999</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>45999</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45210</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>45040</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>46170</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>46170</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>46170</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>46002</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>44968</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45693</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45703</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45706</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45268</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45751</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>46035</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>46032</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>46031</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>46032</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>46034</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45972</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>46036</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>46036</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>46036</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>46036</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>46036</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>46178</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>46038</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>46038</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45189</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>46042</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>46043</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44511</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44518</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>46051</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>45756</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>46051</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>46059</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45301</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>46059</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45327</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>46064</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>46066</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>46070</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>46070</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>46070</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>46070</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45260</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>46086</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>44900</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>46085</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>46091</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45062</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44900</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45751</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45751</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>44950</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>46101</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>44608</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45058</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>46106</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>45253</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>46199</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>45363</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>44960</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>45375</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>46114</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>46114</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>44910</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>45356</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>45210</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>46124</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>46126</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>46126</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>46125</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>46126</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>44713</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>44713</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>46127</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>45826</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>46133</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>46134</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45163</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>46135</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>46134</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>45901</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45237</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>45600</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>44900</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>45375</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>45612</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>46205</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>46205</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45198</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45906</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>46197</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>44791</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>46211</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>45189</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45587</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44917</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>44917</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>46124</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44952</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>45350</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>44517</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>45208</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>46276</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45664</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>46276</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>44865</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>46281</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>44655</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45233</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45751</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>46240</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>44942</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45190</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45273</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>46288</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>46287</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>46246</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>46246</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>46246</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45159</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>46248</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45769</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>46290</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45057</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>46290</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>46290</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45385</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>46287</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>46290</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>44895</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>46252</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>46294</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44811</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>45925</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>45933</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>46296</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45198</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>45491</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>45198</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45782</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46259</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>46260</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45796</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>46307</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45925</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45576</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45800</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45692</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45800</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>46265</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45804</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45804</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>45804</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45253</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>45811</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>45811</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>45233</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45812</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45812</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45817</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45774</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>45616</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>45471</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>46310</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45734</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>46268</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>46269</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>46310</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>46310</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45734</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45573</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45859</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>45625</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45870</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45538</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45776</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45769</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>44628</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45323</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45317</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45345</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45345</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45606</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45373</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45565</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45482</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45323</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46094</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>46093</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>46077</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>

--- a/Översikt VÅRGÅRDA.xlsx
+++ b/Översikt VÅRGÅRDA.xlsx
@@ -601,7 +601,7 @@
         <v>44628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45254</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>44992</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45911</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45937</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>45755</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45752</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>45989</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>46036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>46059</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>46066</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>45203</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>45008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>45757</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>46287</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45752</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>44693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>44568</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44601</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44533</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44496</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44818</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44571</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44501</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44743</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44607</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44580</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44511</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44811</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>44501</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44573</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44662</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44648</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44515</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45040</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45315</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44907</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45751</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>45469</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>44984</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45327</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45329</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>45233</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45357</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45620</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44725</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45363</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44946</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45374</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>45375</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45351</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45247</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45362</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>45443</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45400</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45110</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45189</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44846</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44881</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45357</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45357</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45180</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>45772</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44920</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45446</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>44984</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45565</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44914</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44739</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>46030</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>45354</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44908</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45446</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45397</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45891</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45084</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45180</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>46036</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45443</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44936</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>44568</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45987</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>45852</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>45406</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>44943</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>45910</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45910</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>45910</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>45134</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>45429</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>45429</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>44905</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45772</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45923</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45920</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45920</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45925</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45756</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44984</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45366</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45927</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45105</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>45933</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45932</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45932</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45932</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45933</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45938</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>45084</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>44922</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>45947</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>44951</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>45726</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>45401</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>44964</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>45247</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45715</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45330</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>45397</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45397</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>45212</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>45968</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45968</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45973</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>45972</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>45608</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>45972</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45974</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45112</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45985</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45985</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>45985</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45989</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45988</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45989</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45988</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45406</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>46031</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>46031</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45999</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>45999</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45210</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>45040</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>46170</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>46170</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>46170</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>46002</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>44968</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45693</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45703</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45706</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45268</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45751</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>46035</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>46032</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>46031</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>46032</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>46034</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45972</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>46036</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>46036</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>46036</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>46036</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>46036</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>46178</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>46038</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>46038</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45189</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>46042</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>46043</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44511</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44518</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>46051</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>45756</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>46051</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>46059</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45301</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>46059</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45327</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>46064</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>46066</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>46070</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>46070</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>46070</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>46070</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45260</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>46086</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>44900</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>46085</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>46091</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45062</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44900</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45751</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45751</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>44950</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>46101</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>44608</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45058</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>46106</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>45253</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>46199</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>45363</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>44960</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>45375</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>46114</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>46114</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>44910</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>45356</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>45210</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>46124</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>46126</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>46126</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>46125</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>46126</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>44713</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>44713</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>46127</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>45826</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>46133</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>46134</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45163</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>46135</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>46134</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>45901</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45237</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>45600</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>44900</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>45375</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>45612</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>46205</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>46205</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45198</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45906</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>46197</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>44791</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>46211</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>45189</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45587</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44917</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>44917</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>46124</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44952</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>45350</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>44517</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>45208</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>46276</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45664</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>46276</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>44865</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>46281</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>44655</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45233</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45751</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>46240</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>44942</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45190</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45273</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>46288</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>46287</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>46246</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>46246</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>46246</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45159</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>46248</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45769</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>46290</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45057</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>46290</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>46290</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45385</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>46287</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>46290</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>44895</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>46252</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>46294</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44811</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>45925</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>45933</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>46296</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45198</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>45491</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>45198</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45782</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46259</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>46260</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45796</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>46307</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45925</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45576</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45800</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45692</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45800</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>46265</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45804</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45804</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>45804</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45253</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>45811</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>45811</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>45233</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45812</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45812</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45817</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45774</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>45616</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>45471</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>46310</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45734</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>46268</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>46269</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>46310</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>46310</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45734</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45573</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45859</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>45625</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45870</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45538</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45776</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45769</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>44628</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45323</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45317</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45345</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45345</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45606</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45373</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45565</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45482</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45323</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46094</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>46093</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>46077</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>

--- a/Översikt VÅRGÅRDA.xlsx
+++ b/Översikt VÅRGÅRDA.xlsx
@@ -601,7 +601,7 @@
         <v>44628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45254</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>44992</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45911</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45937</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>45752</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45989</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>46036</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>46287</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>46059</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>46066</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45008</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>45752</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45755</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>44693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>44601</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44533</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44568</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44496</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44818</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44571</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44501</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44743</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44607</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44580</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44511</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44811</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>44501</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44573</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44662</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44648</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44515</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45776</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45397</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>44739</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45058</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>45891</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>45180</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>44984</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45363</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45105</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>44895</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>45375</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45901</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>45852</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>44900</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45330</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>45910</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45910</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>45910</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>44922</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45920</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>45920</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45923</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>45210</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>46170</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>46170</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>46170</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>45927</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>45429</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>45429</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>45247</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>45933</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>45375</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>45932</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>45932</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45932</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45620</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45938</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44952</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>45189</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>45385</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>45772</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>45253</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45400</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>46178</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>45327</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45947</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>45237</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>45664</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>45208</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>45268</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>45084</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44968</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>45273</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>45968</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45968</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45972</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>45972</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45397</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>45397</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>45973</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>45974</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>46199</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>45469</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44517</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>44811</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>45189</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>46205</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>46205</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>45826</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>45985</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45985</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>45985</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>46197</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45988</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45988</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45906</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45315</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>45989</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>45329</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>45989</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>46211</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>46031</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>45443</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>46031</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>45190</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>45999</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>45999</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>45443</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>46124</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>46002</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>45782</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>45247</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44865</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45703</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>45706</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45693</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>46281</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>46032</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>46031</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>46032</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>46034</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>46240</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>46035</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>46036</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>46036</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>46038</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>46036</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>46038</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>46036</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>46036</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>45796</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>46042</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>46287</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45576</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>46288</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>46043</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45800</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>45800</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>46246</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45804</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45804</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45692</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>46051</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>46246</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>46246</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>45804</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>46051</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>46290</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>46290</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>45253</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>46290</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>46290</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45233</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44846</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>46294</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>46059</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>46059</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45812</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45812</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>45811</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45811</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>46064</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>44942</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>46066</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>45616</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45471</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>46070</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>46070</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45774</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>46070</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>46287</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>46070</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45817</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>46248</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>46296</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>46252</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45734</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>46085</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45734</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>46086</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>46091</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45933</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45925</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44920</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45163</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>44984</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44900</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>46101</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>44950</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45573</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>46106</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>46259</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45859</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45357</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45625</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>46114</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>46114</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>46260</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45870</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>46124</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>46125</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>46126</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>46127</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>46126</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>46126</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>46265</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45538</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>46134</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>46134</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>46133</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45769</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>46307</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45356</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45925</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>44900</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>46135</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>46310</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>46310</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46310</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45901</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45446</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>44908</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>45350</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44914</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>46269</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45401</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45751</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>45751</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>46268</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44568</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>45406</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>45972</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>45987</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45354</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45212</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>46036</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>45925</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>44951</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>46030</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44917</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>44917</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>46276</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>46276</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>44905</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>45366</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>44725</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>44936</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>45210</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>45600</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>45112</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>44713</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>44713</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45565</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>44960</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>45608</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>44984</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>45198</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45726</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45491</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>45084</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>44881</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>44943</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45769</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45057</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45751</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45233</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>44791</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>45751</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45351</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45363</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>44510</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>45374</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45375</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44511</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45110</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45357</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45357</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>45062</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45446</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>44910</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>45134</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45715</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>45040</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45040</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>44518</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>45327</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45189</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>45180</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44608</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45587</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>44655</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45233</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>45260</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>45198</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>45198</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45756</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45612</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>45772</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45362</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44907</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45751</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>45159</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>45735</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>45756</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>45301</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44946</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>44964</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45406</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44628</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45323</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45317</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45345</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45345</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45606</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45373</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45565</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45482</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45323</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>46093</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46094</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>46077</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>46316</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>

--- a/Översikt VÅRGÅRDA.xlsx
+++ b/Översikt VÅRGÅRDA.xlsx
@@ -601,7 +601,7 @@
         <v>44628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45254</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>44992</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45911</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45937</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>45752</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45989</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>46036</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>46287</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>46059</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>46066</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45008</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>45752</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45755</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>44693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>44496</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>44601</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44533</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44568</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44496</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44677</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44818</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44571</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44501</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44743</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44607</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44580</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44511</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44811</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44616</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>44501</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44573</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44662</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44648</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44515</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45776</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45397</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>44739</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45058</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>45891</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>45180</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>44984</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45363</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45105</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>44895</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>45375</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45901</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>45852</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>44900</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45330</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>45910</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45910</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>45910</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>44922</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45920</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>45920</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45923</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>45210</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>46170</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>46170</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>46170</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>45927</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>45429</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>45429</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>45247</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>45933</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>45375</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>45932</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>45932</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45932</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45620</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45938</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44952</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>45189</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>45385</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>45772</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>45253</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45400</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>46178</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>45327</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45947</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>45237</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>45664</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>45208</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>45268</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>45084</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44968</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>45273</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>45968</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45968</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45972</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>45972</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45397</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>45397</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>45973</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>45974</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>46199</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>45469</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44517</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>44811</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>45189</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>46205</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>46205</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>45826</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>45985</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45985</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>45985</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>46197</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45988</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45988</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45906</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45315</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>45989</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>45329</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>45989</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>46211</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>46031</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>45443</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>46031</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>45190</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>45999</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>45999</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>45443</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>46124</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>46002</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>45782</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>45247</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44865</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45703</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>45706</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45693</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>46281</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>46032</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>46031</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>46032</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>46034</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>46240</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>46035</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>46036</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>46036</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>46038</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>46036</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>46038</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>46036</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>46036</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>45796</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>46042</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>46287</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45576</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>46288</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>46043</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45800</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>45800</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>46246</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45804</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45804</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45692</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>46051</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>46246</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>46246</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>45804</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>46051</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>46290</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>46290</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>45253</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>46290</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>46290</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45233</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44846</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>46294</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>46059</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>46059</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45812</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45812</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>45811</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45811</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>46064</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>44942</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>46066</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>45616</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45471</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>46070</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>46070</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45774</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>46070</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>46287</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>46070</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45817</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>46248</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>46296</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>46252</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45734</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>46085</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45734</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>46086</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>46091</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45933</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45925</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44920</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45163</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>44984</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44900</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>46101</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>44950</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45573</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>46106</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>46259</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45859</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45357</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45625</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>46114</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>46114</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>46260</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45870</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>46124</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>46125</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>46126</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>46127</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>46126</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>46126</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>46265</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45538</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>46134</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>46134</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>46133</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45769</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>46307</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45356</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45925</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>44900</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>46135</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>46310</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>46310</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46310</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45901</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45446</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>44908</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>45350</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44914</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>46269</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45401</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45751</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>45751</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>46268</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44568</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>45406</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>45972</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>45987</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45354</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45212</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>46036</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>45925</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>44951</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>46030</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44917</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>44917</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>46276</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>46276</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>44905</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>45366</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>44725</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>44936</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>45210</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>45600</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>45112</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>44713</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>44713</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45565</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>44960</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>45608</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>44984</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>45198</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45726</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45491</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>45084</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>44881</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>44943</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45769</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45057</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45751</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45233</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>44791</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>45751</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45351</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45363</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>44510</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>45374</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45375</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44511</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45110</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45357</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45357</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>45062</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45446</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>44910</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>45134</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45715</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>45040</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45040</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>44518</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>45327</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45189</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>45180</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44608</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45587</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>44655</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45233</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>45260</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>45198</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>45198</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45756</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45612</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>45772</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45362</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44907</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45751</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>45159</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>45735</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>45756</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>45301</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44946</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>44964</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45406</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44628</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45323</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45317</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45345</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45345</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45606</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45373</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45565</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45482</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45323</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>46093</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46094</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>46077</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>46316</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
